--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2045,6 +2045,225 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129670372</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Altaime, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>711803</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365170</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129670392</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Altaime, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>711779</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6365170</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2050,7 +2050,7 @@
         <v>129670372</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2263,6 +2263,3093 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129675581</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>711780</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6365159</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129675762</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>711771</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6365150</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Granstubbe.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129675761</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>711770</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6365117</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tallstubbe.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129675764</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>711764</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6365171</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Tallåga, död.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129675572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>711766</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6365058</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129675752</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>711858</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6365169</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Granlåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Granlåga.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129675751</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>711858</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6365124</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Tallåga.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129675562</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>711765</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6365012</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129675575</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>711769</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6365056</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129675579</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>711767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6365144</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129675564</v>
+      </c>
+      <c r="B25" t="n">
+        <v>107085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>711767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6365026</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129675756</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>711804</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6365002</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Högstubbe (kapad?); tidigare spillkråkebohål.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gran, högstubbe.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129675560</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>711778</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6364996</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129675565</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>711767</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6365026</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129675755</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>711805</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6364849</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Tall, död.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129675554</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110676</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>711804</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6365002</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129675548</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>711805</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6364849</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129675749</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>711768</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6365251</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Tallåga.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129675735</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86996</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>711756</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6365015</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129675539</v>
+      </c>
+      <c r="B34" t="n">
+        <v>110676</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>711827</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6364978</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129675558</v>
+      </c>
+      <c r="B35" t="n">
+        <v>110676</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>711793</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6365004</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129675757</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>711768</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6365042</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Även hack på gran 3 m V.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Gran, död.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129675763</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>711780</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6365159</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Tall, stående död.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129675750</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>711842</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6365316</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Tallåga.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129675585</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>711762</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6365170</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129675754</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>711813</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6364845</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Tall, stående levande.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129675528</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>711844</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6365037</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129675570</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98734</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>711762</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6365051</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129675753</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52223), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>711818</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6364935</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Tall, död.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R16" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,6 +2455,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2688,32 +2693,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675572</v>
+        <v>129675762</v>
       </c>
       <c r="B19" t="n">
-        <v>98734</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711766</v>
+        <v>711771</v>
       </c>
       <c r="R19" t="n">
-        <v>6365058</v>
+        <v>6365150</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2761,11 +2766,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2050,7 +2050,7 @@
         <v>129670372</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>129675572</v>
       </c>
       <c r="B16" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>129675761</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129675764</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>129675762</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>129675752</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>129675751</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129675575</v>
       </c>
       <c r="B23" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>129675579</v>
       </c>
       <c r="B24" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>107085</v>
+        <v>107097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>129675756</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675565</v>
+        <v>129675755</v>
       </c>
       <c r="B28" t="n">
-        <v>98734</v>
+        <v>57732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R28" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,32 +3761,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675755</v>
+        <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>98746</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711805</v>
+        <v>711767</v>
       </c>
       <c r="R29" t="n">
-        <v>6364849</v>
+        <v>6365026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3866,7 +3866,7 @@
         <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>110676</v>
+        <v>110688</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129675749</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675735</v>
+        <v>129675539</v>
       </c>
       <c r="B33" t="n">
-        <v>86996</v>
+        <v>110688</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,43 +4185,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711756</v>
+        <v>711827</v>
       </c>
       <c r="R33" t="n">
-        <v>6365015</v>
+        <v>6364978</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4256,11 +4247,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4270,7 +4256,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4290,10 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675539</v>
+        <v>129675558</v>
       </c>
       <c r="B34" t="n">
-        <v>110676</v>
+        <v>110688</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711827</v>
+        <v>711793</v>
       </c>
       <c r="R34" t="n">
-        <v>6364978</v>
+        <v>6365004</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4392,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675558</v>
+        <v>129675735</v>
       </c>
       <c r="B35" t="n">
-        <v>110676</v>
+        <v>87002</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4403,34 +4389,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711793</v>
+        <v>711756</v>
       </c>
       <c r="R35" t="n">
-        <v>6365004</v>
+        <v>6365015</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4465,6 +4460,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129675757</v>
+        <v>129675763</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711768</v>
+        <v>711780</v>
       </c>
       <c r="R36" t="n">
-        <v>6365042</v>
+        <v>6365159</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4567,11 +4567,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Även hack på gran 3 m V.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4583,7 +4578,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Gran, död.</t>
+          <t>Tall, stående död.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4601,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129675763</v>
+        <v>129675757</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4636,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711780</v>
+        <v>711768</v>
       </c>
       <c r="R37" t="n">
-        <v>6365159</v>
+        <v>6365042</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4674,6 +4669,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Även hack på gran 3 m V.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Tall, stående död.</t>
+          <t>Gran, död.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4706,7 +4706,7 @@
         <v>129675750</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>129675754</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129675570</v>
+        <v>129675753</v>
       </c>
       <c r="B42" t="n">
-        <v>98734</v>
+        <v>57732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711762</v>
+        <v>711818</v>
       </c>
       <c r="R42" t="n">
-        <v>6365051</v>
+        <v>6364935</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5217,6 +5217,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5228,7 +5233,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5246,32 +5251,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129675753</v>
+        <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>98746</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5281,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711818</v>
+        <v>711762</v>
       </c>
       <c r="R43" t="n">
-        <v>6364935</v>
+        <v>6365051</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5319,11 +5324,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2050,7 +2050,7 @@
         <v>129670372</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675572</v>
+        <v>129675761</v>
       </c>
       <c r="B16" t="n">
-        <v>98746</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711766</v>
+        <v>711770</v>
       </c>
       <c r="R16" t="n">
-        <v>6365058</v>
+        <v>6365117</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,11 +2455,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2489,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675761</v>
+        <v>129675762</v>
       </c>
       <c r="B17" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711770</v>
+        <v>711771</v>
       </c>
       <c r="R17" t="n">
-        <v>6365117</v>
+        <v>6365150</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2594,7 +2589,7 @@
         <v>129675764</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2693,32 +2688,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>57732</v>
+        <v>98747</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R19" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2766,6 +2761,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
         <v>129675752</v>
       </c>
       <c r="B20" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>129675751</v>
       </c>
       <c r="B21" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,59 +3111,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675575</v>
+        <v>129675564</v>
       </c>
       <c r="B23" t="n">
-        <v>98746</v>
+        <v>107098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R23" t="n">
-        <v>6365056</v>
+        <v>6365026</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3196,11 +3182,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675579</v>
+        <v>129675575</v>
       </c>
       <c r="B24" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3243,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3281,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R24" t="n">
-        <v>6365144</v>
+        <v>6365056</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3317,6 +3298,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,35 +3334,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675564</v>
+        <v>129675579</v>
       </c>
       <c r="B25" t="n">
-        <v>107097</v>
+        <v>98747</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
@@ -3386,7 +3386,7 @@
         <v>711767</v>
       </c>
       <c r="R25" t="n">
-        <v>6365026</v>
+        <v>6365144</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>129675756</v>
       </c>
       <c r="B26" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675755</v>
+        <v>129675554</v>
       </c>
       <c r="B28" t="n">
-        <v>57732</v>
+        <v>110689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R28" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675565</v>
+        <v>129675548</v>
       </c>
       <c r="B29" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R29" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,32 +3863,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675554</v>
+        <v>129675755</v>
       </c>
       <c r="B30" t="n">
-        <v>110688</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711804</v>
+        <v>711805</v>
       </c>
       <c r="R30" t="n">
-        <v>6365002</v>
+        <v>6364849</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675548</v>
+        <v>129675565</v>
       </c>
       <c r="B31" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>711805</v>
+        <v>711767</v>
       </c>
       <c r="R31" t="n">
-        <v>6364849</v>
+        <v>6365026</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4070,7 +4070,7 @@
         <v>129675749</v>
       </c>
       <c r="B32" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129675539</v>
       </c>
       <c r="B33" t="n">
-        <v>110688</v>
+        <v>110689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>129675558</v>
       </c>
       <c r="B34" t="n">
-        <v>110688</v>
+        <v>110689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129675735</v>
       </c>
       <c r="B35" t="n">
-        <v>87002</v>
+        <v>87003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>129675763</v>
       </c>
       <c r="B36" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>129675757</v>
       </c>
       <c r="B37" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129675750</v>
       </c>
       <c r="B38" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>129675754</v>
       </c>
       <c r="B40" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129675753</v>
+        <v>129675570</v>
       </c>
       <c r="B42" t="n">
-        <v>57732</v>
+        <v>98747</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711818</v>
+        <v>711762</v>
       </c>
       <c r="R42" t="n">
-        <v>6364935</v>
+        <v>6365051</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5217,11 +5217,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5228,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5251,32 +5246,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129675570</v>
+        <v>129675753</v>
       </c>
       <c r="B43" t="n">
-        <v>98746</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5286,10 +5281,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711762</v>
+        <v>711818</v>
       </c>
       <c r="R43" t="n">
-        <v>6365051</v>
+        <v>6364935</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,6 +5319,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675554</v>
+        <v>129675755</v>
       </c>
       <c r="B28" t="n">
-        <v>110689</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711804</v>
+        <v>711805</v>
       </c>
       <c r="R28" t="n">
-        <v>6365002</v>
+        <v>6364849</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675548</v>
+        <v>129675565</v>
       </c>
       <c r="B29" t="n">
         <v>98747</v>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711805</v>
+        <v>711767</v>
       </c>
       <c r="R29" t="n">
-        <v>6364849</v>
+        <v>6365026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,32 +3863,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675755</v>
+        <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>110689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R30" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675565</v>
+        <v>129675548</v>
       </c>
       <c r="B31" t="n">
         <v>98747</v>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R31" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129675570</v>
+        <v>129675753</v>
       </c>
       <c r="B42" t="n">
-        <v>98747</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711762</v>
+        <v>711818</v>
       </c>
       <c r="R42" t="n">
-        <v>6365051</v>
+        <v>6364935</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5217,6 +5217,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5228,7 +5233,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5246,32 +5251,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129675753</v>
+        <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>98747</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5281,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711818</v>
+        <v>711762</v>
       </c>
       <c r="R43" t="n">
-        <v>6364935</v>
+        <v>6365051</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5319,11 +5324,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675761</v>
+        <v>129675572</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711770</v>
+        <v>711766</v>
       </c>
       <c r="R16" t="n">
-        <v>6365117</v>
+        <v>6365058</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,6 +2455,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,7 +2489,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675762</v>
+        <v>129675764</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711771</v>
+        <v>711764</v>
       </c>
       <c r="R17" t="n">
-        <v>6365150</v>
+        <v>6365171</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2568,7 +2573,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2586,7 +2591,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675764</v>
+        <v>129675761</v>
       </c>
       <c r="B18" t="n">
         <v>57733</v>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711764</v>
+        <v>711770</v>
       </c>
       <c r="R18" t="n">
-        <v>6365171</v>
+        <v>6365117</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,7 +2675,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2688,32 +2693,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675572</v>
+        <v>129675762</v>
       </c>
       <c r="B19" t="n">
-        <v>98747</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711766</v>
+        <v>711771</v>
       </c>
       <c r="R19" t="n">
-        <v>6365058</v>
+        <v>6365150</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2761,11 +2766,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,32 +2902,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129675751</v>
+        <v>129675562</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711858</v>
+        <v>711765</v>
       </c>
       <c r="R21" t="n">
-        <v>6365124</v>
+        <v>6365012</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2975,11 +2975,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tallåga med spillkråkehack för födosök.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2991,7 +2986,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Tallåga.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3009,32 +3004,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129675562</v>
+        <v>129675751</v>
       </c>
       <c r="B22" t="n">
-        <v>98747</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711765</v>
+        <v>711858</v>
       </c>
       <c r="R22" t="n">
-        <v>6365012</v>
+        <v>6365124</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,6 +3077,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallåga.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3114,7 +3114,7 @@
         <v>129675564</v>
       </c>
       <c r="B23" t="n">
-        <v>107098</v>
+        <v>107103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129675575</v>
       </c>
       <c r="B24" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129675579</v>
       </c>
       <c r="B25" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675755</v>
+        <v>129675565</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711805</v>
+        <v>711767</v>
       </c>
       <c r="R28" t="n">
-        <v>6364849</v>
+        <v>6365026</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675565</v>
+        <v>129675554</v>
       </c>
       <c r="B29" t="n">
-        <v>98747</v>
+        <v>110694</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711767</v>
+        <v>711804</v>
       </c>
       <c r="R29" t="n">
-        <v>6365026</v>
+        <v>6365002</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675554</v>
+        <v>129675548</v>
       </c>
       <c r="B30" t="n">
-        <v>110689</v>
+        <v>98752</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711804</v>
+        <v>711805</v>
       </c>
       <c r="R30" t="n">
-        <v>6365002</v>
+        <v>6364849</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675548</v>
+        <v>129675755</v>
       </c>
       <c r="B31" t="n">
-        <v>98747</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675539</v>
+        <v>129675735</v>
       </c>
       <c r="B33" t="n">
-        <v>110689</v>
+        <v>87008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,34 +4185,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711827</v>
+        <v>711756</v>
       </c>
       <c r="R33" t="n">
-        <v>6364978</v>
+        <v>6365015</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4247,6 +4256,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4256,7 +4270,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4276,10 +4290,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675558</v>
+        <v>129675539</v>
       </c>
       <c r="B34" t="n">
-        <v>110689</v>
+        <v>110694</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4311,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711793</v>
+        <v>711827</v>
       </c>
       <c r="R34" t="n">
-        <v>6365004</v>
+        <v>6364978</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4378,10 +4392,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675735</v>
+        <v>129675558</v>
       </c>
       <c r="B35" t="n">
-        <v>87003</v>
+        <v>110694</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4389,43 +4403,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711756</v>
+        <v>711793</v>
       </c>
       <c r="R35" t="n">
-        <v>6365015</v>
+        <v>6365004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4460,11 +4465,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129675763</v>
+        <v>129675757</v>
       </c>
       <c r="B36" t="n">
         <v>57733</v>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711780</v>
+        <v>711768</v>
       </c>
       <c r="R36" t="n">
-        <v>6365159</v>
+        <v>6365042</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4567,6 +4567,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Även hack på gran 3 m V.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4578,7 +4583,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tall, stående död.</t>
+          <t>Gran, död.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4596,7 +4601,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129675757</v>
+        <v>129675763</v>
       </c>
       <c r="B37" t="n">
         <v>57733</v>
@@ -4631,10 +4636,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711768</v>
+        <v>711780</v>
       </c>
       <c r="R37" t="n">
-        <v>6365042</v>
+        <v>6365159</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4669,11 +4674,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Även hack på gran 3 m V.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gran, död.</t>
+          <t>Tall, stående död.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675572</v>
+        <v>129675761</v>
       </c>
       <c r="B16" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711766</v>
+        <v>711770</v>
       </c>
       <c r="R16" t="n">
-        <v>6365058</v>
+        <v>6365117</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,11 +2455,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2591,7 +2586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675761</v>
+        <v>129675762</v>
       </c>
       <c r="B18" t="n">
         <v>57733</v>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711770</v>
+        <v>711771</v>
       </c>
       <c r="R18" t="n">
-        <v>6365117</v>
+        <v>6365150</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2675,7 +2670,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2693,32 +2688,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R19" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2766,6 +2761,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,32 +2902,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129675562</v>
+        <v>129675751</v>
       </c>
       <c r="B21" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711765</v>
+        <v>711858</v>
       </c>
       <c r="R21" t="n">
-        <v>6365012</v>
+        <v>6365124</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2975,6 +2975,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2986,7 +2991,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3004,32 +3009,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129675751</v>
+        <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711858</v>
+        <v>711765</v>
       </c>
       <c r="R22" t="n">
-        <v>6365124</v>
+        <v>6365012</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3077,11 +3082,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Tallåga med spillkråkehack för födosök.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Tallåga.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3111,45 +3111,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675564</v>
+        <v>129675575</v>
       </c>
       <c r="B23" t="n">
-        <v>107103</v>
+        <v>98752</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R23" t="n">
-        <v>6365026</v>
+        <v>6365056</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3182,6 +3196,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,7 +3232,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675575</v>
+        <v>129675579</v>
       </c>
       <c r="B24" t="n">
         <v>98752</v>
@@ -3243,7 +3262,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3262,10 +3281,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R24" t="n">
-        <v>6365056</v>
+        <v>6365144</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3298,11 +3317,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,49 +3348,35 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675579</v>
+        <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>98752</v>
+        <v>107103</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
@@ -3386,7 +3386,7 @@
         <v>711767</v>
       </c>
       <c r="R25" t="n">
-        <v>6365144</v>
+        <v>6365026</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675565</v>
+        <v>129675755</v>
       </c>
       <c r="B28" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R28" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675554</v>
+        <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>110694</v>
+        <v>98752</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711804</v>
+        <v>711767</v>
       </c>
       <c r="R29" t="n">
-        <v>6365002</v>
+        <v>6365026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675548</v>
+        <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>98752</v>
+        <v>110694</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R30" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675755</v>
+        <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129675757</v>
+        <v>129675763</v>
       </c>
       <c r="B36" t="n">
         <v>57733</v>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711768</v>
+        <v>711780</v>
       </c>
       <c r="R36" t="n">
-        <v>6365042</v>
+        <v>6365159</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4567,11 +4567,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Även hack på gran 3 m V.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4583,7 +4578,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Gran, död.</t>
+          <t>Tall, stående död.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4601,7 +4596,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129675763</v>
+        <v>129675757</v>
       </c>
       <c r="B37" t="n">
         <v>57733</v>
@@ -4636,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711780</v>
+        <v>711768</v>
       </c>
       <c r="R37" t="n">
-        <v>6365159</v>
+        <v>6365042</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4674,6 +4669,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Även hack på gran 3 m V.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Tall, stående död.</t>
+          <t>Gran, död.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,7 +2382,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675761</v>
+        <v>129675762</v>
       </c>
       <c r="B16" t="n">
         <v>57733</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711770</v>
+        <v>711771</v>
       </c>
       <c r="R16" t="n">
-        <v>6365117</v>
+        <v>6365150</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675764</v>
+        <v>129675761</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711764</v>
+        <v>711770</v>
       </c>
       <c r="R17" t="n">
-        <v>6365171</v>
+        <v>6365117</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675762</v>
+        <v>129675764</v>
       </c>
       <c r="B18" t="n">
         <v>57733</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711771</v>
+        <v>711764</v>
       </c>
       <c r="R18" t="n">
-        <v>6365150</v>
+        <v>6365171</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2902,32 +2902,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129675751</v>
+        <v>129675562</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711858</v>
+        <v>711765</v>
       </c>
       <c r="R21" t="n">
-        <v>6365124</v>
+        <v>6365012</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2975,11 +2975,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tallåga med spillkråkehack för födosök.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2991,7 +2986,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Tallåga.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3009,32 +3004,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129675562</v>
+        <v>129675751</v>
       </c>
       <c r="B22" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711765</v>
+        <v>711858</v>
       </c>
       <c r="R22" t="n">
-        <v>6365012</v>
+        <v>6365124</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,6 +3077,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallåga.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675755</v>
+        <v>129675565</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711805</v>
+        <v>711767</v>
       </c>
       <c r="R28" t="n">
-        <v>6364849</v>
+        <v>6365026</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675565</v>
+        <v>129675548</v>
       </c>
       <c r="B29" t="n">
         <v>98752</v>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R29" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,32 +3863,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675554</v>
+        <v>129675755</v>
       </c>
       <c r="B30" t="n">
-        <v>110694</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711804</v>
+        <v>711805</v>
       </c>
       <c r="R30" t="n">
-        <v>6365002</v>
+        <v>6364849</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675548</v>
+        <v>129675554</v>
       </c>
       <c r="B31" t="n">
-        <v>98752</v>
+        <v>110694</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R31" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675539</v>
+        <v>129675558</v>
       </c>
       <c r="B34" t="n">
         <v>110694</v>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711827</v>
+        <v>711793</v>
       </c>
       <c r="R34" t="n">
-        <v>6364978</v>
+        <v>6365004</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675558</v>
+        <v>129675539</v>
       </c>
       <c r="B35" t="n">
         <v>110694</v>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711793</v>
+        <v>711827</v>
       </c>
       <c r="R35" t="n">
-        <v>6365004</v>
+        <v>6364978</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R16" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,6 +2455,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2688,32 +2693,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675572</v>
+        <v>129675762</v>
       </c>
       <c r="B19" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711766</v>
+        <v>711771</v>
       </c>
       <c r="R19" t="n">
-        <v>6365058</v>
+        <v>6365150</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2761,11 +2766,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,32 +2902,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129675562</v>
+        <v>129675751</v>
       </c>
       <c r="B21" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711765</v>
+        <v>711858</v>
       </c>
       <c r="R21" t="n">
-        <v>6365012</v>
+        <v>6365124</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2975,6 +2975,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2986,7 +2991,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3004,32 +3009,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129675751</v>
+        <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711858</v>
+        <v>711765</v>
       </c>
       <c r="R22" t="n">
-        <v>6365124</v>
+        <v>6365012</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3077,11 +3082,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Tallåga med spillkråkehack för födosök.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Tallåga.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675548</v>
+        <v>129675554</v>
       </c>
       <c r="B29" t="n">
-        <v>98752</v>
+        <v>110694</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R29" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,32 +3863,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675755</v>
+        <v>129675548</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>98752</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675554</v>
+        <v>129675755</v>
       </c>
       <c r="B31" t="n">
-        <v>110694</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>711804</v>
+        <v>711805</v>
       </c>
       <c r="R31" t="n">
-        <v>6365002</v>
+        <v>6364849</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675558</v>
+        <v>129675539</v>
       </c>
       <c r="B34" t="n">
         <v>110694</v>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711793</v>
+        <v>711827</v>
       </c>
       <c r="R34" t="n">
-        <v>6365004</v>
+        <v>6364978</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675539</v>
+        <v>129675558</v>
       </c>
       <c r="B35" t="n">
         <v>110694</v>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711827</v>
+        <v>711793</v>
       </c>
       <c r="R35" t="n">
-        <v>6364978</v>
+        <v>6365004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675572</v>
+        <v>129675761</v>
       </c>
       <c r="B16" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711766</v>
+        <v>711770</v>
       </c>
       <c r="R16" t="n">
-        <v>6365058</v>
+        <v>6365117</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,11 +2455,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2489,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675761</v>
+        <v>129675764</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711770</v>
+        <v>711764</v>
       </c>
       <c r="R17" t="n">
-        <v>6365117</v>
+        <v>6365171</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2591,7 +2586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675764</v>
+        <v>129675762</v>
       </c>
       <c r="B18" t="n">
         <v>57733</v>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711764</v>
+        <v>711771</v>
       </c>
       <c r="R18" t="n">
-        <v>6365171</v>
+        <v>6365150</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2675,7 +2670,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2693,32 +2688,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>98756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R19" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2766,6 +2761,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129675575</v>
       </c>
       <c r="B23" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>129675579</v>
       </c>
       <c r="B24" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>107103</v>
+        <v>107107</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675565</v>
+        <v>129675755</v>
       </c>
       <c r="B28" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R28" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675554</v>
+        <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>110694</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711804</v>
+        <v>711767</v>
       </c>
       <c r="R29" t="n">
-        <v>6365002</v>
+        <v>6365026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675548</v>
+        <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>98752</v>
+        <v>110698</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R30" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675755</v>
+        <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675735</v>
+        <v>129675539</v>
       </c>
       <c r="B33" t="n">
-        <v>87008</v>
+        <v>110698</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,43 +4185,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711756</v>
+        <v>711827</v>
       </c>
       <c r="R33" t="n">
-        <v>6365015</v>
+        <v>6364978</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4256,11 +4247,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4270,7 +4256,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4290,10 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675539</v>
+        <v>129675558</v>
       </c>
       <c r="B34" t="n">
-        <v>110694</v>
+        <v>110698</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711827</v>
+        <v>711793</v>
       </c>
       <c r="R34" t="n">
-        <v>6364978</v>
+        <v>6365004</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4392,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675558</v>
+        <v>129675735</v>
       </c>
       <c r="B35" t="n">
-        <v>110694</v>
+        <v>87012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4403,34 +4389,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711793</v>
+        <v>711756</v>
       </c>
       <c r="R35" t="n">
-        <v>6365004</v>
+        <v>6365015</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4465,6 +4460,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4926,45 +4926,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129675754</v>
+        <v>129675528</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711813</v>
+        <v>711844</v>
       </c>
       <c r="R40" t="n">
-        <v>6364845</v>
+        <v>6365037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,7 +5024,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Tall, stående levande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5028,59 +5042,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129675528</v>
+        <v>129675754</v>
       </c>
       <c r="B41" t="n">
-        <v>98752</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711844</v>
+        <v>711813</v>
       </c>
       <c r="R41" t="n">
-        <v>6365037</v>
+        <v>6364845</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, stående levande.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
         <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675761</v>
+        <v>129675764</v>
       </c>
       <c r="B16" t="n">
         <v>57733</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711770</v>
+        <v>711764</v>
       </c>
       <c r="R16" t="n">
-        <v>6365117</v>
+        <v>6365171</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675764</v>
+        <v>129675761</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711764</v>
+        <v>711770</v>
       </c>
       <c r="R17" t="n">
-        <v>6365171</v>
+        <v>6365117</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
         <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675575</v>
+        <v>129675579</v>
       </c>
       <c r="B23" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R23" t="n">
-        <v>6365056</v>
+        <v>6365144</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3196,11 +3196,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,10 +3227,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675579</v>
+        <v>129675575</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3257,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3281,10 +3276,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R24" t="n">
-        <v>6365144</v>
+        <v>6365056</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3317,6 +3312,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3351,7 +3351,7 @@
         <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>107107</v>
+        <v>107109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675565</v>
+        <v>129675548</v>
       </c>
       <c r="B29" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R29" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675554</v>
+        <v>129675565</v>
       </c>
       <c r="B30" t="n">
-        <v>110698</v>
+        <v>98758</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711804</v>
+        <v>711767</v>
       </c>
       <c r="R30" t="n">
-        <v>6365002</v>
+        <v>6365026</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675548</v>
+        <v>129675554</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>110700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R31" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675539</v>
+        <v>129675735</v>
       </c>
       <c r="B33" t="n">
-        <v>110698</v>
+        <v>87014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,34 +4185,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711827</v>
+        <v>711756</v>
       </c>
       <c r="R33" t="n">
-        <v>6364978</v>
+        <v>6365015</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4247,6 +4256,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4256,7 +4270,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4279,7 +4293,7 @@
         <v>129675558</v>
       </c>
       <c r="B34" t="n">
-        <v>110698</v>
+        <v>110700</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4378,10 +4392,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675735</v>
+        <v>129675539</v>
       </c>
       <c r="B35" t="n">
-        <v>87012</v>
+        <v>110700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4389,43 +4403,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711756</v>
+        <v>711827</v>
       </c>
       <c r="R35" t="n">
-        <v>6365015</v>
+        <v>6364978</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4460,11 +4465,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129675763</v>
+        <v>129675757</v>
       </c>
       <c r="B36" t="n">
         <v>57733</v>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711780</v>
+        <v>711768</v>
       </c>
       <c r="R36" t="n">
-        <v>6365159</v>
+        <v>6365042</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4567,6 +4567,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Även hack på gran 3 m V.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4578,7 +4583,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tall, stående död.</t>
+          <t>Gran, död.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4596,7 +4601,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129675757</v>
+        <v>129675763</v>
       </c>
       <c r="B37" t="n">
         <v>57733</v>
@@ -4631,10 +4636,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711768</v>
+        <v>711780</v>
       </c>
       <c r="R37" t="n">
-        <v>6365042</v>
+        <v>6365159</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4669,11 +4674,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Även hack på gran 3 m V.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gran, död.</t>
+          <t>Tall, stående död.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4926,59 +4926,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129675528</v>
+        <v>129675754</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711844</v>
+        <v>711813</v>
       </c>
       <c r="R40" t="n">
-        <v>6365037</v>
+        <v>6364845</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5024,7 +5010,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, stående levande.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5042,45 +5028,59 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129675754</v>
+        <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>98758</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711813</v>
+        <v>711844</v>
       </c>
       <c r="R41" t="n">
-        <v>6364845</v>
+        <v>6365037</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Tall, stående levande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
         <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675764</v>
+        <v>129675761</v>
       </c>
       <c r="B16" t="n">
         <v>57733</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711764</v>
+        <v>711770</v>
       </c>
       <c r="R16" t="n">
-        <v>6365171</v>
+        <v>6365117</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675761</v>
+        <v>129675764</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711770</v>
+        <v>711764</v>
       </c>
       <c r="R17" t="n">
-        <v>6365117</v>
+        <v>6365171</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
         <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2902,32 +2902,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129675751</v>
+        <v>129675562</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711858</v>
+        <v>711765</v>
       </c>
       <c r="R21" t="n">
-        <v>6365124</v>
+        <v>6365012</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2975,11 +2975,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tallåga med spillkråkehack för födosök.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2991,7 +2986,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Tallåga.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3009,32 +3004,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129675562</v>
+        <v>129675751</v>
       </c>
       <c r="B22" t="n">
-        <v>98758</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711765</v>
+        <v>711858</v>
       </c>
       <c r="R22" t="n">
-        <v>6365012</v>
+        <v>6365124</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3082,6 +3077,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallåga.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3114,7 +3114,7 @@
         <v>129675579</v>
       </c>
       <c r="B23" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,59 +3227,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675575</v>
+        <v>129675564</v>
       </c>
       <c r="B24" t="n">
-        <v>98758</v>
+        <v>107119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R24" t="n">
-        <v>6365056</v>
+        <v>6365026</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3312,11 +3298,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,45 +3329,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675564</v>
+        <v>129675575</v>
       </c>
       <c r="B25" t="n">
-        <v>107109</v>
+        <v>98768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R25" t="n">
-        <v>6365026</v>
+        <v>6365056</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3419,6 +3414,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675548</v>
+        <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711805</v>
+        <v>711767</v>
       </c>
       <c r="R29" t="n">
-        <v>6364849</v>
+        <v>6365026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675565</v>
+        <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>98758</v>
+        <v>110735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711767</v>
+        <v>711804</v>
       </c>
       <c r="R30" t="n">
-        <v>6365026</v>
+        <v>6365002</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675554</v>
+        <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>110700</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>711804</v>
+        <v>711805</v>
       </c>
       <c r="R31" t="n">
-        <v>6365002</v>
+        <v>6364849</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675735</v>
+        <v>129675539</v>
       </c>
       <c r="B33" t="n">
-        <v>87014</v>
+        <v>110735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,43 +4185,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711756</v>
+        <v>711827</v>
       </c>
       <c r="R33" t="n">
-        <v>6365015</v>
+        <v>6364978</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4256,11 +4247,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4270,7 +4256,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4293,7 +4279,7 @@
         <v>129675558</v>
       </c>
       <c r="B34" t="n">
-        <v>110700</v>
+        <v>110735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675539</v>
+        <v>129675735</v>
       </c>
       <c r="B35" t="n">
-        <v>110700</v>
+        <v>87014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4403,34 +4389,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711827</v>
+        <v>711756</v>
       </c>
       <c r="R35" t="n">
-        <v>6364978</v>
+        <v>6365015</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4465,6 +4460,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129675757</v>
+        <v>129675763</v>
       </c>
       <c r="B36" t="n">
         <v>57733</v>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711768</v>
+        <v>711780</v>
       </c>
       <c r="R36" t="n">
-        <v>6365042</v>
+        <v>6365159</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4567,11 +4567,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Även hack på gran 3 m V.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4583,7 +4578,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Gran, död.</t>
+          <t>Tall, stående död.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4601,7 +4596,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129675763</v>
+        <v>129675757</v>
       </c>
       <c r="B37" t="n">
         <v>57733</v>
@@ -4636,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711780</v>
+        <v>711768</v>
       </c>
       <c r="R37" t="n">
-        <v>6365159</v>
+        <v>6365042</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4674,6 +4669,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Även hack på gran 3 m V.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Tall, stående död.</t>
+          <t>Gran, död.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4926,45 +4926,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129675754</v>
+        <v>129675528</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711813</v>
+        <v>711844</v>
       </c>
       <c r="R40" t="n">
-        <v>6364845</v>
+        <v>6365037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,7 +5024,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Tall, stående levande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5028,59 +5042,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129675528</v>
+        <v>129675754</v>
       </c>
       <c r="B41" t="n">
-        <v>98758</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711844</v>
+        <v>711813</v>
       </c>
       <c r="R41" t="n">
-        <v>6365037</v>
+        <v>6364845</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, stående levande.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129675753</v>
+        <v>129675570</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711818</v>
+        <v>711762</v>
       </c>
       <c r="R42" t="n">
-        <v>6364935</v>
+        <v>6365051</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5217,11 +5217,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5228,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5251,32 +5246,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129675570</v>
+        <v>129675753</v>
       </c>
       <c r="B43" t="n">
-        <v>98758</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5286,10 +5281,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711762</v>
+        <v>711818</v>
       </c>
       <c r="R43" t="n">
-        <v>6365051</v>
+        <v>6364935</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,6 +5319,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675761</v>
+        <v>129675572</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711770</v>
+        <v>711766</v>
       </c>
       <c r="R16" t="n">
-        <v>6365117</v>
+        <v>6365058</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,6 +2455,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,7 +2489,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675764</v>
+        <v>129675761</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711764</v>
+        <v>711770</v>
       </c>
       <c r="R17" t="n">
-        <v>6365171</v>
+        <v>6365117</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2568,7 +2573,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2586,7 +2591,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675762</v>
+        <v>129675764</v>
       </c>
       <c r="B18" t="n">
         <v>57733</v>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711771</v>
+        <v>711764</v>
       </c>
       <c r="R18" t="n">
-        <v>6365150</v>
+        <v>6365171</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,7 +2675,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2688,32 +2693,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675572</v>
+        <v>129675762</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711766</v>
+        <v>711771</v>
       </c>
       <c r="R19" t="n">
-        <v>6365058</v>
+        <v>6365150</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2761,11 +2766,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675572</v>
+        <v>129675761</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711766</v>
+        <v>711770</v>
       </c>
       <c r="R16" t="n">
-        <v>6365058</v>
+        <v>6365117</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,11 +2455,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2489,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675761</v>
+        <v>129675764</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711770</v>
+        <v>711764</v>
       </c>
       <c r="R17" t="n">
-        <v>6365117</v>
+        <v>6365171</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2591,7 +2586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675764</v>
+        <v>129675762</v>
       </c>
       <c r="B18" t="n">
         <v>57733</v>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711764</v>
+        <v>711771</v>
       </c>
       <c r="R18" t="n">
-        <v>6365171</v>
+        <v>6365150</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2675,7 +2670,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2693,32 +2688,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R19" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2766,6 +2761,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,32 +2902,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129675562</v>
+        <v>129675751</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711765</v>
+        <v>711858</v>
       </c>
       <c r="R21" t="n">
-        <v>6365012</v>
+        <v>6365124</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2975,6 +2975,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tallåga med spillkråkehack för födosök.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2986,7 +2991,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3004,32 +3009,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129675751</v>
+        <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711858</v>
+        <v>711765</v>
       </c>
       <c r="R22" t="n">
-        <v>6365124</v>
+        <v>6365012</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3077,11 +3082,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Tallåga med spillkråkehack för födosök.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Tallåga.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4926,59 +4926,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129675528</v>
+        <v>129675754</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711844</v>
+        <v>711813</v>
       </c>
       <c r="R40" t="n">
-        <v>6365037</v>
+        <v>6364845</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5024,7 +5010,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, stående levande.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5042,45 +5028,59 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129675754</v>
+        <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711813</v>
+        <v>711844</v>
       </c>
       <c r="R41" t="n">
-        <v>6364845</v>
+        <v>6365037</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Tall, stående levande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129675570</v>
+        <v>129675753</v>
       </c>
       <c r="B42" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711762</v>
+        <v>711818</v>
       </c>
       <c r="R42" t="n">
-        <v>6365051</v>
+        <v>6364935</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5217,6 +5217,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5228,7 +5233,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5246,32 +5251,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129675753</v>
+        <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>98768</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5281,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711818</v>
+        <v>711762</v>
       </c>
       <c r="R43" t="n">
-        <v>6364935</v>
+        <v>6365051</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5319,11 +5324,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2050,7 +2050,7 @@
         <v>129670372</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675761</v>
+        <v>129675572</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711770</v>
+        <v>711766</v>
       </c>
       <c r="R16" t="n">
-        <v>6365117</v>
+        <v>6365058</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,6 +2455,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675764</v>
+        <v>129675761</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711764</v>
+        <v>711770</v>
       </c>
       <c r="R17" t="n">
-        <v>6365171</v>
+        <v>6365117</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2568,7 +2573,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2586,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675762</v>
+        <v>129675764</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711771</v>
+        <v>711764</v>
       </c>
       <c r="R18" t="n">
-        <v>6365150</v>
+        <v>6365171</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,7 +2675,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2688,32 +2693,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675572</v>
+        <v>129675762</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>57734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711766</v>
+        <v>711771</v>
       </c>
       <c r="R19" t="n">
-        <v>6365058</v>
+        <v>6365150</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2761,11 +2766,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
         <v>129675752</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>129675751</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675579</v>
+        <v>129675575</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R23" t="n">
-        <v>6365144</v>
+        <v>6365056</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3196,6 +3196,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,35 +3232,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675564</v>
+        <v>129675579</v>
       </c>
       <c r="B24" t="n">
-        <v>107119</v>
+        <v>98772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
@@ -3265,7 +3284,7 @@
         <v>711767</v>
       </c>
       <c r="R24" t="n">
-        <v>6365026</v>
+        <v>6365144</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3329,59 +3348,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675575</v>
+        <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>107123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R25" t="n">
-        <v>6365056</v>
+        <v>6365026</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3414,11 +3419,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,7 +3453,7 @@
         <v>129675756</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>129675755</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129675749</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675539</v>
+        <v>129675735</v>
       </c>
       <c r="B33" t="n">
-        <v>110735</v>
+        <v>87017</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,34 +4185,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711827</v>
+        <v>711756</v>
       </c>
       <c r="R33" t="n">
-        <v>6364978</v>
+        <v>6365015</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4247,6 +4256,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4256,7 +4270,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4276,10 +4290,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675558</v>
+        <v>129675539</v>
       </c>
       <c r="B34" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4311,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711793</v>
+        <v>711827</v>
       </c>
       <c r="R34" t="n">
-        <v>6365004</v>
+        <v>6364978</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4378,10 +4392,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675735</v>
+        <v>129675558</v>
       </c>
       <c r="B35" t="n">
-        <v>87014</v>
+        <v>110739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4389,43 +4403,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711756</v>
+        <v>711793</v>
       </c>
       <c r="R35" t="n">
-        <v>6365015</v>
+        <v>6365004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4460,11 +4465,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4497,7 +4497,7 @@
         <v>129675763</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>129675757</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129675750</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>129675754</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>129675753</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675572</v>
+        <v>129675761</v>
       </c>
       <c r="B16" t="n">
-        <v>98772</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711766</v>
+        <v>711770</v>
       </c>
       <c r="R16" t="n">
-        <v>6365058</v>
+        <v>6365117</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,11 +2455,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2489,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675761</v>
+        <v>129675764</v>
       </c>
       <c r="B17" t="n">
         <v>57734</v>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711770</v>
+        <v>711764</v>
       </c>
       <c r="R17" t="n">
-        <v>6365117</v>
+        <v>6365171</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2591,7 +2586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675764</v>
+        <v>129675762</v>
       </c>
       <c r="B18" t="n">
         <v>57734</v>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711764</v>
+        <v>711771</v>
       </c>
       <c r="R18" t="n">
-        <v>6365171</v>
+        <v>6365150</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2675,7 +2670,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2693,32 +2688,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>57734</v>
+        <v>98772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R19" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2766,6 +2761,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2050,7 +2050,7 @@
         <v>129670372</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>129675761</v>
       </c>
       <c r="B16" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129675764</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>129675762</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>129675752</v>
       </c>
       <c r="B20" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>129675751</v>
       </c>
       <c r="B21" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129675575</v>
       </c>
       <c r="B23" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>129675579</v>
       </c>
       <c r="B24" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>107123</v>
+        <v>107126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>129675756</v>
       </c>
       <c r="B26" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675755</v>
+        <v>129675565</v>
       </c>
       <c r="B28" t="n">
-        <v>57734</v>
+        <v>98775</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711805</v>
+        <v>711767</v>
       </c>
       <c r="R28" t="n">
-        <v>6364849</v>
+        <v>6365026</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675565</v>
+        <v>129675554</v>
       </c>
       <c r="B29" t="n">
-        <v>98772</v>
+        <v>110742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711767</v>
+        <v>711804</v>
       </c>
       <c r="R29" t="n">
-        <v>6365026</v>
+        <v>6365002</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675554</v>
+        <v>129675548</v>
       </c>
       <c r="B30" t="n">
-        <v>110739</v>
+        <v>98775</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711804</v>
+        <v>711805</v>
       </c>
       <c r="R30" t="n">
-        <v>6365002</v>
+        <v>6364849</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675548</v>
+        <v>129675755</v>
       </c>
       <c r="B31" t="n">
-        <v>98772</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
         <v>129675749</v>
       </c>
       <c r="B32" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675735</v>
+        <v>129675539</v>
       </c>
       <c r="B33" t="n">
-        <v>87017</v>
+        <v>110742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,43 +4185,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711756</v>
+        <v>711827</v>
       </c>
       <c r="R33" t="n">
-        <v>6365015</v>
+        <v>6364978</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4256,11 +4247,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4270,7 +4256,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4290,10 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675539</v>
+        <v>129675558</v>
       </c>
       <c r="B34" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711827</v>
+        <v>711793</v>
       </c>
       <c r="R34" t="n">
-        <v>6364978</v>
+        <v>6365004</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4392,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675558</v>
+        <v>129675735</v>
       </c>
       <c r="B35" t="n">
-        <v>110739</v>
+        <v>87020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4403,34 +4389,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711793</v>
+        <v>711756</v>
       </c>
       <c r="R35" t="n">
-        <v>6365004</v>
+        <v>6365015</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4465,6 +4460,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4497,7 +4497,7 @@
         <v>129675763</v>
       </c>
       <c r="B36" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>129675757</v>
       </c>
       <c r="B37" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129675750</v>
       </c>
       <c r="B38" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>129675754</v>
       </c>
       <c r="B40" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>129675753</v>
       </c>
       <c r="B42" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -4926,45 +4926,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129675754</v>
+        <v>129675528</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>98775</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711813</v>
+        <v>711844</v>
       </c>
       <c r="R40" t="n">
-        <v>6364845</v>
+        <v>6365037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,7 +5024,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Tall, stående levande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5028,59 +5042,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129675528</v>
+        <v>129675754</v>
       </c>
       <c r="B41" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711844</v>
+        <v>711813</v>
       </c>
       <c r="R41" t="n">
-        <v>6365037</v>
+        <v>6364845</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, stående levande.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -3659,32 +3659,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129675565</v>
+        <v>129675755</v>
       </c>
       <c r="B28" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711767</v>
+        <v>711805</v>
       </c>
       <c r="R28" t="n">
-        <v>6365026</v>
+        <v>6364849</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129675554</v>
+        <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>110742</v>
+        <v>98775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>711804</v>
+        <v>711767</v>
       </c>
       <c r="R29" t="n">
-        <v>6365002</v>
+        <v>6365026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129675548</v>
+        <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>98775</v>
+        <v>110742</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711805</v>
+        <v>711804</v>
       </c>
       <c r="R30" t="n">
-        <v>6364849</v>
+        <v>6365002</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129675755</v>
+        <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>98775</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4926,59 +4926,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129675528</v>
+        <v>129675754</v>
       </c>
       <c r="B40" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711844</v>
+        <v>711813</v>
       </c>
       <c r="R40" t="n">
-        <v>6365037</v>
+        <v>6364845</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5024,7 +5010,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, stående levande.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5042,45 +5028,59 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129675754</v>
+        <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>98775</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711813</v>
+        <v>711844</v>
       </c>
       <c r="R41" t="n">
-        <v>6364845</v>
+        <v>6365037</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Tall, stående levande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129675753</v>
+        <v>129675570</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>98775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711818</v>
+        <v>711762</v>
       </c>
       <c r="R42" t="n">
-        <v>6364935</v>
+        <v>6365051</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5217,11 +5217,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5228,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5251,32 +5246,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129675570</v>
+        <v>129675753</v>
       </c>
       <c r="B43" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5286,10 +5281,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711762</v>
+        <v>711818</v>
       </c>
       <c r="R43" t="n">
-        <v>6365051</v>
+        <v>6364935</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,6 +5319,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2162,7 +2162,7 @@
         <v>129670392</v>
       </c>
       <c r="B14" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675761</v>
+        <v>129675572</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>98776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711770</v>
+        <v>711766</v>
       </c>
       <c r="R16" t="n">
-        <v>6365117</v>
+        <v>6365058</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,6 +2455,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,7 +2489,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675764</v>
+        <v>129675761</v>
       </c>
       <c r="B17" t="n">
         <v>57737</v>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711764</v>
+        <v>711770</v>
       </c>
       <c r="R17" t="n">
-        <v>6365171</v>
+        <v>6365117</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2568,7 +2573,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2586,7 +2591,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675762</v>
+        <v>129675764</v>
       </c>
       <c r="B18" t="n">
         <v>57737</v>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711771</v>
+        <v>711764</v>
       </c>
       <c r="R18" t="n">
-        <v>6365150</v>
+        <v>6365171</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,7 +2675,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2688,32 +2693,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675572</v>
+        <v>129675762</v>
       </c>
       <c r="B19" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711766</v>
+        <v>711771</v>
       </c>
       <c r="R19" t="n">
-        <v>6365058</v>
+        <v>6365150</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2761,11 +2766,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,59 +3111,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675575</v>
+        <v>129675564</v>
       </c>
       <c r="B23" t="n">
-        <v>98775</v>
+        <v>107127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R23" t="n">
-        <v>6365056</v>
+        <v>6365026</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3196,11 +3182,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675579</v>
+        <v>129675575</v>
       </c>
       <c r="B24" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3243,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3281,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R24" t="n">
-        <v>6365144</v>
+        <v>6365056</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3317,6 +3298,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,35 +3334,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675564</v>
+        <v>129675579</v>
       </c>
       <c r="B25" t="n">
-        <v>107126</v>
+        <v>98776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
@@ -3386,7 +3386,7 @@
         <v>711767</v>
       </c>
       <c r="R25" t="n">
-        <v>6365026</v>
+        <v>6365144</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129675539</v>
       </c>
       <c r="B33" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>129675558</v>
       </c>
       <c r="B34" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129675735</v>
       </c>
       <c r="B35" t="n">
-        <v>87020</v>
+        <v>87021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>129675528</v>
       </c>
       <c r="B41" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129675570</v>
+        <v>129675753</v>
       </c>
       <c r="B42" t="n">
-        <v>98775</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711762</v>
+        <v>711818</v>
       </c>
       <c r="R42" t="n">
-        <v>6365051</v>
+        <v>6364935</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5217,6 +5217,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5228,7 +5233,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, död.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5246,32 +5251,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129675753</v>
+        <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>98776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5281,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711818</v>
+        <v>711762</v>
       </c>
       <c r="R43" t="n">
-        <v>6364935</v>
+        <v>6365051</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5319,11 +5324,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Död tall med spillkråkehack. Utgångshål insekter.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Tall, död.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2382,32 +2382,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129675572</v>
+        <v>129675761</v>
       </c>
       <c r="B16" t="n">
-        <v>98776</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711766</v>
+        <v>711770</v>
       </c>
       <c r="R16" t="n">
-        <v>6365058</v>
+        <v>6365117</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2455,11 +2455,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallstubbe.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2489,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129675761</v>
+        <v>129675764</v>
       </c>
       <c r="B17" t="n">
         <v>57737</v>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711770</v>
+        <v>711764</v>
       </c>
       <c r="R17" t="n">
-        <v>6365117</v>
+        <v>6365171</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,7 +2568,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallstubbe.</t>
+          <t>Tallåga, död.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2591,7 +2586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129675764</v>
+        <v>129675762</v>
       </c>
       <c r="B18" t="n">
         <v>57737</v>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711764</v>
+        <v>711771</v>
       </c>
       <c r="R18" t="n">
-        <v>6365171</v>
+        <v>6365150</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2675,7 +2670,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallåga, död.</t>
+          <t>Granstubbe.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2693,32 +2688,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129675762</v>
+        <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>98776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711771</v>
+        <v>711766</v>
       </c>
       <c r="R19" t="n">
-        <v>6365150</v>
+        <v>6365058</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2766,6 +2761,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd i skogen.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granstubbe.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3111,45 +3111,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675564</v>
+        <v>129675575</v>
       </c>
       <c r="B23" t="n">
-        <v>107127</v>
+        <v>98776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R23" t="n">
-        <v>6365026</v>
+        <v>6365056</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3182,6 +3196,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,7 +3232,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675575</v>
+        <v>129675579</v>
       </c>
       <c r="B24" t="n">
         <v>98776</v>
@@ -3243,7 +3262,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3262,10 +3281,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R24" t="n">
-        <v>6365056</v>
+        <v>6365144</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3298,11 +3317,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,49 +3348,35 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675579</v>
+        <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>98776</v>
+        <v>107127</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
@@ -3386,7 +3386,7 @@
         <v>711767</v>
       </c>
       <c r="R25" t="n">
-        <v>6365144</v>
+        <v>6365026</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -3111,59 +3111,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675575</v>
+        <v>129675564</v>
       </c>
       <c r="B23" t="n">
-        <v>98776</v>
+        <v>107127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R23" t="n">
-        <v>6365056</v>
+        <v>6365026</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3196,11 +3182,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,7 +3213,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675579</v>
+        <v>129675575</v>
       </c>
       <c r="B24" t="n">
         <v>98776</v>
@@ -3262,7 +3243,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3281,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R24" t="n">
-        <v>6365144</v>
+        <v>6365056</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3317,6 +3298,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,35 +3334,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675564</v>
+        <v>129675579</v>
       </c>
       <c r="B25" t="n">
-        <v>107127</v>
+        <v>98776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
@@ -3386,7 +3386,7 @@
         <v>711767</v>
       </c>
       <c r="R25" t="n">
-        <v>6365026</v>
+        <v>6365144</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 52223-2025 artfynd.xlsx
+++ b/artfynd/A 52223-2025 artfynd.xlsx
@@ -2269,7 +2269,7 @@
         <v>129675581</v>
       </c>
       <c r="B15" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129675572</v>
       </c>
       <c r="B19" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>129675562</v>
       </c>
       <c r="B22" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,45 +3111,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129675564</v>
+        <v>129675575</v>
       </c>
       <c r="B23" t="n">
-        <v>107127</v>
+        <v>98793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711767</v>
+        <v>711769</v>
       </c>
       <c r="R23" t="n">
-        <v>6365026</v>
+        <v>6365056</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3182,6 +3196,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,10 +3232,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129675575</v>
+        <v>129675579</v>
       </c>
       <c r="B24" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3262,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3262,10 +3281,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711769</v>
+        <v>711767</v>
       </c>
       <c r="R24" t="n">
-        <v>6365056</v>
+        <v>6365144</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3298,11 +3317,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,49 +3348,35 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129675579</v>
+        <v>129675564</v>
       </c>
       <c r="B25" t="n">
-        <v>98776</v>
+        <v>107144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
@@ -3386,7 +3386,7 @@
         <v>711767</v>
       </c>
       <c r="R25" t="n">
-        <v>6365144</v>
+        <v>6365026</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3560,7 +3560,7 @@
         <v>129675560</v>
       </c>
       <c r="B27" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129675565</v>
       </c>
       <c r="B29" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>129675554</v>
       </c>
       <c r="B30" t="n">
-        <v>110743</v>
+        <v>110760</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129675548</v>
       </c>
       <c r="B31" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129675539</v>
+        <v>129675735</v>
       </c>
       <c r="B33" t="n">
-        <v>110743</v>
+        <v>87038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4185,34 +4185,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219677</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711827</v>
+        <v>711756</v>
       </c>
       <c r="R33" t="n">
-        <v>6364978</v>
+        <v>6365015</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4247,6 +4256,11 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Artsorakel identifiering.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4256,7 +4270,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4276,10 +4290,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129675558</v>
+        <v>129675539</v>
       </c>
       <c r="B34" t="n">
-        <v>110743</v>
+        <v>110760</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4311,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711793</v>
+        <v>711827</v>
       </c>
       <c r="R34" t="n">
-        <v>6365004</v>
+        <v>6364978</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4378,10 +4392,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129675735</v>
+        <v>129675558</v>
       </c>
       <c r="B35" t="n">
-        <v>87021</v>
+        <v>110760</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4389,43 +4403,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>219677</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711756</v>
+        <v>711793</v>
       </c>
       <c r="R35" t="n">
-        <v>6365015</v>
+        <v>6365004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4460,11 +4465,6 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Artsorakel identifiering.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Kalkbarrskog.</t>
         </is>
@@ -4813,7 +4813,7 @@
         <v>129675585</v>
       </c>
       <c r="B39" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4926,45 +4926,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129675754</v>
+        <v>129675528</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>98793</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711813</v>
+        <v>711844</v>
       </c>
       <c r="R40" t="n">
-        <v>6364845</v>
+        <v>6365037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,7 +5024,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Tall, stående levande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5028,59 +5042,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129675528</v>
+        <v>129675754</v>
       </c>
       <c r="B41" t="n">
-        <v>98776</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Altajme 1:35 (A 52223), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711844</v>
+        <v>711813</v>
       </c>
       <c r="R41" t="n">
-        <v>6365037</v>
+        <v>6364845</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tall, stående levande.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
         <v>129675570</v>
       </c>
       <c r="B43" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
